--- a/nr-update-patient-gender/ig/StructureDefinition-fr-core-organization-external.xlsx
+++ b/nr-update-patient-gender/ig/StructureDefinition-fr-core-organization-external.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T08:43:01+00:00</t>
+    <t>2025-10-08T11:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient-gender/ig/StructureDefinition-fr-core-organization-external.xlsx
+++ b/nr-update-patient-gender/ig/StructureDefinition-fr-core-organization-external.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T11:52:57+00:00</t>
+    <t>2025-10-08T11:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
